--- a/users.xlsx
+++ b/users.xlsx
@@ -1,23 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7160"/>
+    <workbookView windowWidth="19200" windowHeight="7160"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="Users" state="visible" r:id="rId4"/>
+    <sheet name="Users" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Users!$A$1:$L$82</definedName>
     <definedName name="_xlnm._FilterDatabase">Users!$A$1:$L$80</definedName>
   </definedNames>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="903" uniqueCount="325">
   <si>
     <t>SrNo</t>
   </si>
@@ -971,64 +985,257 @@
   </si>
   <si>
     <t>Qurat@1122</t>
+  </si>
+  <si>
+    <t>Rimsha</t>
+  </si>
+  <si>
+    <t>7185_19707_OR</t>
+  </si>
+  <si>
+    <t>@Rimsha786</t>
+  </si>
+  <si>
+    <t>Uc-106/Asianwala</t>
+  </si>
+  <si>
+    <t>Muhammad Rizwan</t>
+  </si>
+  <si>
+    <t>14011_19807_OR</t>
+  </si>
+  <si>
+    <t>Shahdat@2021</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="42" formatCode="_-&quot;£&quot;* #,##0_-;\-&quot;£&quot;* #,##0_-;_-&quot;£&quot;* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;£&quot;* #,##0.00_-;\-&quot;£&quot;* #,##0.00_-;_-&quot;£&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="30">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <family val="2"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
       <charset val="134"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
-      <name val="Arial"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Arial"/>
-    </font>
-    <font>
       <charset val="134"/>
-      <sz val="6"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
       <charset val="134"/>
-      <sz val="8"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
+      <sz val="8"/>
+      <name val="Arial"/>
       <charset val="134"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="9"/>
-      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
       <charset val="134"/>
-      <color theme="0"/>
-      <sz val="9"/>
-      <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1039,11 +1246,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -1064,8 +1266,194 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1090,22 +1478,17 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFBDD7EE"/>
+        <color auto="1"/>
       </left>
-      <right style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top style="thin">
         <color rgb="FFBDD7EE"/>
       </top>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin">
-        <color rgb="FFBDD7EE"/>
-      </top>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1125,23 +1508,279 @@
       <left style="thin">
         <color rgb="FFBDD7EE"/>
       </left>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1152,35 +1791,81 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1469,9 +2154,10 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L81"/>
-  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="9" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L83"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
     <col min="2" max="3" width="12" customWidth="1"/>
@@ -1484,7 +2170,7 @@
     <col min="12" max="12" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1522,7 +2208,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1560,7 +2246,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1598,7 +2284,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1636,7 +2322,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1674,7 +2360,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1712,7 +2398,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1750,7 +2436,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -1788,7 +2474,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1826,7 +2512,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -1864,7 +2550,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1902,7 +2588,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -1940,7 +2626,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1978,7 +2664,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -2016,7 +2702,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -2054,7 +2740,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -2092,7 +2778,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -2130,7 +2816,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -2168,7 +2854,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -2206,7 +2892,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -2244,7 +2930,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -2282,7 +2968,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -2320,7 +3006,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -2358,7 +3044,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -2396,7 +3082,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -2434,7 +3120,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -2472,7 +3158,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -2510,7 +3196,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -2548,7 +3234,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -2586,7 +3272,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -2624,7 +3310,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -2662,7 +3348,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -2700,7 +3386,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -2738,7 +3424,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -2776,7 +3462,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -2814,7 +3500,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -2852,7 +3538,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -2890,7 +3576,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -2928,7 +3614,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -2966,7 +3652,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -3004,7 +3690,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -3042,7 +3728,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -3080,7 +3766,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -3118,7 +3804,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -3156,7 +3842,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -3194,7 +3880,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -3232,7 +3918,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -3270,7 +3956,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -3308,7 +3994,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -3346,7 +4032,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -3384,7 +4070,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -3422,7 +4108,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -3460,7 +4146,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -3498,7 +4184,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -3536,7 +4222,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -3574,7 +4260,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -3612,7 +4298,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -3650,7 +4336,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -3688,7 +4374,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -3726,7 +4412,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -3764,7 +4450,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -3802,7 +4488,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -3840,7 +4526,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -3878,7 +4564,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -3916,7 +4602,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -3954,7 +4640,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -3992,7 +4678,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -4030,7 +4716,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -4068,7 +4754,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -4106,7 +4792,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -4144,7 +4830,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -4182,7 +4868,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -4220,7 +4906,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -4258,7 +4944,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -4296,7 +4982,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -4334,7 +5020,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -4372,7 +5058,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -4410,7 +5096,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -4448,7 +5134,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -4486,7 +5172,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -4496,10 +5182,10 @@
       <c r="C80" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="E80" s="4" t="s">
+      <c r="E80" s="3" t="s">
         <v>312</v>
       </c>
       <c r="F80" s="4" t="s">
@@ -4524,7 +5210,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -4562,8 +5248,57 @@
         <v>17</v>
       </c>
     </row>
+    <row r="82" customHeight="1" spans="1:12">
+      <c r="A82" s="2">
+        <v>81</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E82" t="s">
+        <v>318</v>
+      </c>
+      <c r="F82" t="s">
+        <v>319</v>
+      </c>
+      <c r="G82" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="1:12">
+      <c r="A83" s="2">
+        <v>82</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>321</v>
+      </c>
+      <c r="E83" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="F83" s="11" t="s">
+        <v>323</v>
+      </c>
+      <c r="G83" s="12" t="s">
+        <v>324</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L81"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L82" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="G83" r:id="rId1" display="Shahdat@2021"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>